--- a/src/main/resources/docs/code/common-code_v1.xlsx
+++ b/src/main/resources/docs/code/common-code_v1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,163 +45,172 @@
     <t>CO_USER_STATUS</t>
   </si>
   <si>
+    <t>LOCK</t>
+  </si>
+  <si>
+    <t>WITHDRAW</t>
+  </si>
+  <si>
+    <t>탈퇴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코드명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO_ROLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADMIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MANAGER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매니저</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반사용자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO_PERMISSION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>READ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPDATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELETE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO_MENU_TYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCREEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POPUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LINK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO_JOB_TYPE</t>
+  </si>
+  <si>
+    <t>LOGIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOGOUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팝업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메뉴 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그아웃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹코드명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역할</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행위 권한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO_USER_STATUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO_JOB_TYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>NORMAL</t>
-  </si>
-  <si>
-    <t>LOCK</t>
-  </si>
-  <si>
-    <t>WITHDRAW</t>
-  </si>
-  <si>
-    <t>탈퇴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코드명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CO_ROLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADMIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MANAGER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>USER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠금</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>매니저</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반사용자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CO_PERMISSION</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>READ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CREATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UPDATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DELETE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CO_MENU_TYPE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCREEN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POPUP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LINK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CO_JOB_TYPE</t>
-  </si>
-  <si>
-    <t>LOGIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOGOUT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조회</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>삭제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>팝업</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>링크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메뉴 타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그아웃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹코드명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용자 상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이벤트 타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>역할</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>행위 권한</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -594,13 +603,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>3</v>
@@ -611,16 +620,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -634,13 +643,13 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1">
         <v>2</v>
@@ -654,13 +663,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
@@ -671,16 +680,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -691,16 +700,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2">
         <v>2</v>
@@ -711,16 +720,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
@@ -731,16 +740,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -751,16 +760,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -771,16 +780,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -791,16 +800,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
@@ -811,16 +820,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -831,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -851,16 +860,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
@@ -871,16 +880,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -891,16 +900,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
@@ -911,16 +920,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="2">
         <v>3</v>
@@ -931,16 +940,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" s="2">
         <v>4</v>
@@ -951,16 +960,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" s="2">
         <v>5</v>
